--- a/output/pdf_financials_xlsx/ARIC.xlsx
+++ b/output/pdf_financials_xlsx/ARIC.xlsx
@@ -793,10 +793,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.284526</v>
       </c>
     </row>
     <row r="35">
@@ -805,10 +803,8 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -817,10 +813,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.284526</v>
       </c>
     </row>
     <row r="37">
@@ -829,10 +823,8 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -841,10 +833,8 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -853,10 +843,8 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -865,10 +853,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>7e-06</v>
       </c>
     </row>
     <row r="41">
@@ -877,10 +863,8 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>7e-06</v>
       </c>
     </row>
     <row r="42">
@@ -889,10 +873,8 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -901,10 +883,8 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -913,10 +893,8 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -925,10 +903,8 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -937,10 +913,8 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -949,10 +923,8 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -961,10 +933,8 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -973,10 +943,8 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>0.284533</v>
       </c>
     </row>
     <row r="50">
@@ -985,10 +953,8 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -997,10 +963,8 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1009,10 +973,8 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1021,10 +983,8 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1033,10 +993,8 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1057,10 +1015,8 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1069,10 +1025,8 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1081,10 +1035,8 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1093,10 +1045,8 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1105,10 +1055,8 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1117,10 +1065,8 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1153,10 +1099,8 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1165,10 +1109,8 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1177,10 +1119,8 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1189,10 +1129,8 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1201,10 +1139,8 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.016096</v>
       </c>
     </row>
     <row r="69">
@@ -1213,10 +1149,8 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1225,10 +1159,8 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1237,10 +1169,8 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1249,10 +1179,8 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1261,10 +1189,8 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1273,10 +1199,8 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1285,10 +1209,8 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1309,10 +1231,8 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1321,10 +1241,8 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1333,10 +1251,8 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1357,10 +1273,8 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1369,10 +1283,8 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1381,10 +1293,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1393,10 +1303,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1405,10 +1313,8 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1441,10 +1347,8 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="89">
@@ -1453,10 +1357,8 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1477,10 +1379,8 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1489,10 +1389,8 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1501,10 +1399,8 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1513,10 +1409,8 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>0.268437</v>
       </c>
     </row>
     <row r="95">
@@ -1525,10 +1419,8 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1537,10 +1429,8 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.268437</v>
       </c>
     </row>
     <row r="97">
@@ -1947,7 +1837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1986,89 +1876,99 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Net loss for the period $ (47,837) $</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Cash $ 398,270 $</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E2" s="5" t="n">
-        <v>-0.031563</v>
+        <v>0.284526</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Share-based compensation 16,431</t>
+          <t>GST receivable 2,213</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>7e-06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Increase in GST receivable (2,206)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Current total</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="n">
-        <v>-7e-06</v>
+        <v>0.284533</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Increase (decrease) in accounts payable and accrued liabilities (3,260)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities $ 12,836 $</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n">
         <v>0.016096</v>
       </c>
@@ -2076,124 +1976,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cash used in operating activities (36,872)</t>
+          <t>Share capital – Note 6 $ 445,002 $</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.015474</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Issuance of common shares 200,000</t>
+          <t>Reserves 22,045</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0.3</v>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Share issuance costs (49,384)</t>
+          <t>Deficit (79,400)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="5" t="n">
+        <v>-0.031563</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cash provided by financing activities 150,616</t>
+          <t>SHAREHOLDERS’ EQUITY total</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.3</v>
+        <v>0.268437</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Increase in cash 113,744</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Going Concern - Note</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" s="5" t="n">
-        <v>0.284526</v>
+        <v>2e-06</v>
       </c>
     </row>
     <row r="11">
@@ -2204,23 +2100,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cash, beginning of the period 284,526</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the period $ (47,837) $</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>-0.031563</v>
       </c>
     </row>
     <row r="12">
@@ -2231,21 +2121,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cash, end of the period $ 398,270 $</t>
+          <t>Share-based compensation 16,431</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0.284526</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -2256,19 +2148,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Supplemental disclosure of cash flow information</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Interest paid in cash $ - $</t>
+          <t>Increase in GST receivable (2,206)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="5" t="n">
+        <v>-7e-06</v>
       </c>
     </row>
     <row r="14">
@@ -2279,232 +2169,238 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Supplemental disclosure of cash flow information</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Income taxes paid in cash $ - $</t>
+          <t>Increase (decrease) in accounts payable and accrued liabilities (3,260)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="5" t="n">
+        <v>0.016096</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Listing fees $ 18,707 $</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Cash used in operating activities (36,872)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
-        <v>0.018948</v>
+        <v>-0.015474</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Share-based compensation – Note 6 16,431</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Issuance of common shares 200,000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Audit and accounting fees 8,000</t>
+          <t>Share issuance costs (49,384)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" s="5" t="n">
-        <v>0.005</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Consulting fees 2,740</t>
+          <t>Cash provided by financing activities 150,616</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Legal fees 1,831</t>
+          <t>Increase in cash 113,744</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.007418</v>
+        <v>0.284526</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bank charges 128</t>
+          <t>Cash, beginning of the period 284,526</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>0.000197</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period $ (47,837) $</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Cash, end of the period $ 398,270 $</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
-        <v>-0.031563</v>
+        <v>0.284526</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Supplemental disclosure of cash flow information</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding 7,426,231</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>2.890053</v>
+          <t>Interest paid in cash $ - $</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Supplemental disclosure of cash flow information</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $ (0.01) $</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>-1e-08</v>
+          <t>Income taxes paid in cash $ - $</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2515,19 +2411,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Balance at June 23, 2015 - $ - $ - $ - $</t>
+          <t>Listing fees $ 18,707 $</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" s="5" t="n">
+        <v>0.018948</v>
       </c>
     </row>
     <row r="25">
@@ -2538,12 +2432,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Share issued 1 - - -</t>
+          <t>Share-based compensation – Note 6 16,431</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2561,17 +2455,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Private placement 6,000,000 300,000 - -</t>
+          <t>Audit and accounting fees 8,000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="5" t="n">
-        <v>0.3</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="27">
@@ -2582,17 +2476,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the period - - - (31,563)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" s="5" t="n">
-        <v>-0.031563</v>
+          <t>Consulting fees 2,740</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -2603,17 +2503,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2015 6,000,001 $ 300,000 $ - $ (31,563) $</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Legal fees 1,831</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
-        <v>0.268437</v>
+        <v>0.007418</v>
       </c>
     </row>
     <row r="29">
@@ -2624,17 +2528,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Initial public offering 2,000,000 200,000 - -</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Bank charges 128</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
-        <v>0.2</v>
+        <v>0.000197</v>
       </c>
     </row>
     <row r="30">
@@ -2645,17 +2553,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Share issuance costs – Note 6 - (54,998) 5,614 -</t>
+          <t>Net loss and comprehensive loss for the period $ (47,837) $</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="5" t="n">
-        <v>-0.049384</v>
+        <v>-0.031563</v>
       </c>
     </row>
     <row r="31">
@@ -2666,17 +2574,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Share-based compensation – Note 6 - - 16,431 -</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding 7,426,231</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
-        <v>0.016431</v>
+        <v>2.890053</v>
       </c>
     </row>
     <row r="32">
@@ -2687,17 +2599,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year - - - (47,837)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Basic and diluted loss per share $ (0.01) $</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
-        <v>-0.047837</v>
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="33">
@@ -2713,11 +2629,204 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Balance at June 23, 2015 - $ - $ - $ - $</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Share issued 1 - - -</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Private placement 6,000,000 300,000 - -</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" s="5" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Comprehensive loss for the period - - - (31,563)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" s="5" t="n">
+        <v>-0.031563</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Balance at December 31, 2015 6,000,001 $ 300,000 $ - $ (31,563) $</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" s="5" t="n">
+        <v>0.268437</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Initial public offering 2,000,000 200,000 - -</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Share issuance costs – Note 6 - (54,998) 5,614 -</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" s="5" t="n">
+        <v>-0.049384</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Share-based compensation – Note 6 - - 16,431 -</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" s="5" t="n">
+        <v>0.016431</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Comprehensive loss for the year - - - (47,837)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" s="5" t="n">
+        <v>-0.047837</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Shares   Share Capital       Reserves          Deficit               Total</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>Balance at December 31, 2016 8,000,001 $ 445,002 $ 22,045 $ (79,400) $</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" s="5" t="n">
         <v>0.387647</v>
       </c>
     </row>
